--- a/Semestr 4/Cad/2ME-PCBLAB/Michal_Wojna/Lab_4_schematic/tabela_impedancji.xlsx
+++ b/Semestr 4/Cad/2ME-PCBLAB/Michal_Wojna/Lab_4_schematic/tabela_impedancji.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\Desktop\Git\aghmtm\Semestr 4\Cad\2ME-PCBLAB\Michal_Wojna\Lab_4_schematic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D82E2521-D3A4-4752-97CE-3C07709AFA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C3AD43-FA9C-48C9-8448-14C2500BED67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -511,46 +511,56 @@
         <v>8</v>
       </c>
       <c r="D4" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E4" s="3">
         <v>4</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="F4" s="3">
+        <v>13</v>
+      </c>
+      <c r="G4" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="3">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3">
         <v>8</v>
       </c>
       <c r="D5" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E5" s="3">
         <v>4</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="F5" s="3">
+        <v>11</v>
+      </c>
+      <c r="G5" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="3">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="F6" s="3">
+        <v>13</v>
+      </c>
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
@@ -558,14 +568,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="3">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="F7" s="3">
+        <v>11</v>
+      </c>
       <c r="G7" s="3"/>
     </row>
   </sheetData>

--- a/Semestr 4/Cad/2ME-PCBLAB/Michal_Wojna/Lab_4_schematic/tabela_impedancji.xlsx
+++ b/Semestr 4/Cad/2ME-PCBLAB/Michal_Wojna/Lab_4_schematic/tabela_impedancji.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\Desktop\Git\aghmtm\Semestr 4\Cad\2ME-PCBLAB\Michal_Wojna\Lab_4_schematic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C3AD43-FA9C-48C9-8448-14C2500BED67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF506A6-9D10-4242-BE36-B364621D12FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t>Low-tech</t>
   </si>
@@ -33,9 +33,6 @@
   <si>
     <t>Z [Ohms]
 (dla minimalnych wymiarów)</t>
-  </si>
-  <si>
-    <t>Ω</t>
   </si>
   <si>
     <t>W [mil]</t>
@@ -66,6 +63,15 @@
 Z = 50 Ω
 TS 4 warstwy,
 1mm</t>
+  </si>
+  <si>
+    <t>154Ω</t>
+  </si>
+  <si>
+    <t>159Ω</t>
+  </si>
+  <si>
+    <t>158Ω</t>
   </si>
 </sst>
 </file>
@@ -467,45 +473,45 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="F3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3">
         <v>8</v>
@@ -517,7 +523,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="3">
         <v>3</v>
@@ -525,10 +531,10 @@
     </row>
     <row r="5" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3">
         <v>8</v>
@@ -540,7 +546,7 @@
         <v>4</v>
       </c>
       <c r="F5" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="3">
         <v>3</v>
@@ -548,35 +554,35 @@
     </row>
     <row r="6" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G7" s="3"/>
     </row>

--- a/Semestr 4/Cad/2ME-PCBLAB/Michal_Wojna/Lab_4_schematic/tabela_impedancji.xlsx
+++ b/Semestr 4/Cad/2ME-PCBLAB/Michal_Wojna/Lab_4_schematic/tabela_impedancji.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\Desktop\Git\aghmtm\Semestr 4\Cad\2ME-PCBLAB\Michal_Wojna\Lab_4_schematic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF506A6-9D10-4242-BE36-B364621D12FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F56AEF6-B865-44A5-815B-2855CA6C6132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="13583" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Zestawienie Impedancji" sheetId="1" r:id="rId1"/>
@@ -65,13 +65,13 @@
 1mm</t>
   </si>
   <si>
-    <t>154Ω</t>
-  </si>
-  <si>
-    <t>159Ω</t>
-  </si>
-  <si>
-    <t>158Ω</t>
+    <t>79.4Ω</t>
+  </si>
+  <si>
+    <t>102Ω</t>
+  </si>
+  <si>
+    <t>111Ω</t>
   </si>
 </sst>
 </file>
